--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5B80E3-D749-4DB0-8745-649FEBE9045B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514F9B2D-8F8D-4232-9CB7-0AEE71DAB9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="uITextMessage" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -54,6 +65,63 @@
   <si>
     <t>Space, Enter, Left Click... 
 To advance the conversation.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>W,A,S,D　or　I,J,K,L…移動
+Shift, +キー…ダッシュ
+マウス移動…視点移動
+左クリック…インタラクト
+右クリック or E or U…アイテム使用
+F or H…ライト点滅
+P or Z…ポーズ/ポーズ解除/戻るCtrl, ?キー…振り返る</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリア時間</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Clear time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夢想</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夢幻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪夢</t>
+    <rPh sb="0" eb="2">
+      <t>アクム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Reverie</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Phantasm</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nightmare</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>W, A, S, D or I, J, K, L… Move
+Shift, + key… Dash
+Mouse movement… 
+Camera movement
+Left click… Interact
+Right click or E or U… Use item
+F or H… Flashing light
+P or Z… Pause/Unpause/Back
+Ctrl, ? key… Turn around</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -425,29 +493,89 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="300">
       <c r="A3">
         <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>16</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
         <v>4</v>
       </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
         <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5">

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514F9B2D-8F8D-4232-9CB7-0AEE71DAB9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F59A16D-6AC2-42D4-8CA5-7512091A9238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F59A16D-6AC2-42D4-8CA5-7512091A9238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BB6E47-78B2-428B-90DA-545D071186E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -122,6 +122,25 @@
 F or H… Flashing light
 P or Z… Pause/Unpause/Back
 Ctrl, ? key… Turn around</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>memo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ReturnToTitlePanel内</t>
+    <rPh sb="18" eb="19">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルへ戻りますか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Return to title?</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -450,16 +469,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
     <col min="3" max="3" width="22.625" customWidth="1"/>
     <col min="4" max="4" width="17.625" customWidth="1"/>
     <col min="5" max="5" width="18.875" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -475,8 +495,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="75">
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -493,7 +516,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="300">
+    <row r="3" spans="1:6" ht="300">
       <c r="A3">
         <v>1</v>
       </c>
@@ -510,7 +533,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -527,7 +550,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -544,7 +567,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -561,7 +584,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -578,47 +601,62 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BB6E47-78B2-428B-90DA-545D071186E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2968A2-012B-42F7-84B4-571AF44D4D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -141,6 +141,22 @@
   </si>
   <si>
     <t>Return to title?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デモ版をプレイしていただきありがとうございます!
+X(@Tomanegi0707)・BlueSky(@tomanegi0707.bsky.social)で
+随時最新情報をお知らせしていきます！
+アンケートの回答とSNSのフォロー、
+ウィッシュリスト登録していただけますと幸いです！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Thank you for playing the demo version!
+We'll be sharing the latest updates regularly on
+X (@Tomanegi0707) and BlueSky (@tomanegi0707.bsky.social)!
+We would really appreciate it if you could fill out the survey, 
+follow us on SNS, and add the game to your Wishlist!</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -621,9 +637,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" ht="337.5">
       <c r="A9">
         <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -635,6 +663,7 @@
       <c r="A11">
         <v>9</v>
       </c>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2968A2-012B-42F7-84B4-571AF44D4D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B37D848-49CD-45E3-9B20-6D76952D2859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,16 +68,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>W,A,S,D　or　I,J,K,L…移動
-Shift, +キー…ダッシュ
-マウス移動…視点移動
-左クリック…インタラクト
-右クリック or E or U…アイテム使用
-F or H…ライト点滅
-P or Z…ポーズ/ポーズ解除/戻るCtrl, ?キー…振り返る</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>クリア時間</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -157,6 +147,17 @@
 X (@Tomanegi0707) and BlueSky (@tomanegi0707.bsky.social)!
 We would really appreciate it if you could fill out the survey, 
 follow us on SNS, and add the game to your Wishlist!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>W,A,S,D　or　I,J,K,L…移動
+Shift, +キー…ダッシュ
+マウス移動…視点移動
+左クリック…インタラクト
+右クリック or E or U…アイテム使用
+F or H…ライト点滅
+P or Z…ポーズ/ポーズ解除/戻る
+Ctrl, ?キー…振り返る</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -512,7 +513,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="75">
@@ -537,13 +538,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -554,13 +555,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>16</v>
@@ -571,13 +572,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -588,13 +589,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>32</v>
@@ -605,13 +606,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>32</v>
@@ -622,19 +623,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <v>14</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="337.5">
@@ -642,13 +643,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>24</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <v>24</v>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B37D848-49CD-45E3-9B20-6D76952D2859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C368B7-C1BE-4415-9A9B-5B536A854B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C368B7-C1BE-4415-9A9B-5B536A854B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8B7834-B18B-4F5E-8B8B-7F02D3358956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -646,13 +646,13 @@
         <v>20</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6">

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8B7834-B18B-4F5E-8B8B-7F02D3358956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E6AADE-2EA1-46D5-B6DF-CE95E70BA09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,6 +103,52 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>memo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ReturnToTitlePanel内</t>
+    <rPh sb="18" eb="19">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルへ戻りますか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Return to title?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デモ版をプレイしていただきありがとうございます!
+X(@Tomanegi0707)・BlueSky(@tomanegi0707.bsky.social)で
+随時最新情報をお知らせしていきます！
+アンケートの回答とSNSのフォロー、
+ウィッシュリスト登録していただけますと幸いです！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Thank you for playing the demo version!
+We'll be sharing the latest updates regularly on
+X (@Tomanegi0707) and BlueSky (@tomanegi0707.bsky.social)!
+We would really appreciate it if you could fill out the survey, 
+follow us on SNS, and add the game to your Wishlist!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>W,A,S,D　or　I,J,K,L…移動
+Shift, +キー…ダッシュ
+マウス移動…視点移動
+左クリック…インタラクト
+右クリック or E or U…アイテム使用
+F or H…ライト点滅
+P or Z or ESC…ポーズ/ポーズ解除/戻る
+Ctrl, ?キー…振り返る</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>W, A, S, D or I, J, K, L… Move
 Shift, + key… Dash
 Mouse movement… 
@@ -110,54 +156,8 @@
 Left click… Interact
 Right click or E or U… Use item
 F or H… Flashing light
-P or Z… Pause/Unpause/Back
+P or Z or ESC… Pause/Unpause/Back
 Ctrl, ? key… Turn around</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>memo</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ReturnToTitlePanel内</t>
-    <rPh sb="18" eb="19">
-      <t>ナイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイトルへ戻りますか？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Return to title?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デモ版をプレイしていただきありがとうございます!
-X(@Tomanegi0707)・BlueSky(@tomanegi0707.bsky.social)で
-随時最新情報をお知らせしていきます！
-アンケートの回答とSNSのフォロー、
-ウィッシュリスト登録していただけますと幸いです！</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Thank you for playing the demo version!
-We'll be sharing the latest updates regularly on
-X (@Tomanegi0707) and BlueSky (@tomanegi0707.bsky.social)!
-We would really appreciate it if you could fill out the survey, 
-follow us on SNS, and add the game to your Wishlist!</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>W,A,S,D　or　I,J,K,L…移動
-Shift, +キー…ダッシュ
-マウス移動…視点移動
-左クリック…インタラクト
-右クリック or E or U…アイテム使用
-F or H…ライト点滅
-P or Z…ポーズ/ポーズ解除/戻る
-Ctrl, ?キー…振り返る</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -513,7 +513,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="75">
@@ -538,13 +538,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -623,19 +623,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8">
         <v>14</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="337.5">
@@ -643,13 +643,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>20</v>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E6AADE-2EA1-46D5-B6DF-CE95E70BA09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A795F3BE-2875-40B1-928D-CC2CF8C0ACC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -547,7 +547,7 @@
         <v>22</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6">

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A795F3BE-2875-40B1-928D-CC2CF8C0ACC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D4BCAE-CF64-42E2-B1FF-3CC2A8A708A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -160,12 +160,56 @@
 Ctrl, ? key… Turn around</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Space、Enter、鼠标左键…
+推进对话</t>
+  </si>
+  <si>
+    <t>W、A、S、D　或　I、J、K、L…移动
+Shift、+键…冲刺
+鼠标移动…视角移动
+鼠标左键…互动
+鼠标右键 或 E 或 U…使用道具
+F 或 H…开关灯光
+P 或 Z 或 ESC…暂停/取消暂停/返回
+Ctrl、?键…回头</t>
+  </si>
+  <si>
+    <t>通关时间</t>
+  </si>
+  <si>
+    <t>梦想</t>
+  </si>
+  <si>
+    <t>梦幻</t>
+  </si>
+  <si>
+    <t>噩梦</t>
+  </si>
+  <si>
+    <t>要返回标题画面吗？</t>
+  </si>
+  <si>
+    <t>感谢您游玩本作的试玩版！
+我们会通过X(@Tomanegi0707)和BlueSky(@tomanegi0707.bsky.social)
+随时发布最新消息！
+如果您能填写问卷、关注我们的社交账号，
+并将本作加入愿望单，我们将不胜感激！</t>
+  </si>
+  <si>
+    <t>messageChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +223,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -201,11 +251,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -486,17 +540,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
     <col min="3" max="3" width="22.625" customWidth="1"/>
     <col min="4" max="4" width="17.625" customWidth="1"/>
     <col min="5" max="5" width="18.875" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
+    <col min="6" max="6" width="22.125" customWidth="1"/>
+    <col min="7" max="7" width="21.75" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,11 +568,17 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="75">
+    <row r="2" spans="1:8" ht="84">
       <c r="A2">
         <v>0</v>
       </c>
@@ -532,8 +594,14 @@
       <c r="E2">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="300">
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="397.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -549,8 +617,14 @@
       <c r="E3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>2</v>
       </c>
@@ -566,8 +640,14 @@
       <c r="E4">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>3</v>
       </c>
@@ -583,8 +663,14 @@
       <c r="E5">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>4</v>
       </c>
@@ -600,8 +686,14 @@
       <c r="E6">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>5</v>
       </c>
@@ -617,8 +709,14 @@
       <c r="E7">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="56.25">
+      <c r="F7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -634,11 +732,17 @@
       <c r="E8">
         <v>14</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="3">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="337.5">
+    <row r="9" spans="1:8" ht="409.6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -654,39 +758,45 @@
       <c r="E9">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D4BCAE-CF64-42E2-B1FF-3CC2A8A708A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114EE9BB-2CA8-4F13-A413-5B2E1157B137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -204,12 +204,56 @@
     <t>messageSizeChinese01</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Space、Enter、滑鼠左鍵…
+推進對話</t>
+  </si>
+  <si>
+    <t>W、A、S、D　或　I、J、K、L…移動
+Shift、+鍵…衝刺
+滑鼠移動…視角移動
+滑鼠左鍵…互動
+滑鼠右鍵 或 E 或 U…使用道具
+F 或 H…開關燈光
+P 或 Z 或 ESC…暫停/取消暫停/返回
+Ctrl、?鍵…回頭</t>
+  </si>
+  <si>
+    <t>通關時間</t>
+  </si>
+  <si>
+    <t>夢想</t>
+  </si>
+  <si>
+    <t>夢幻</t>
+  </si>
+  <si>
+    <t>噩夢</t>
+  </si>
+  <si>
+    <t>要返回標題畫面嗎？</t>
+  </si>
+  <si>
+    <t>感謝您遊玩本作的試玩版！
+我們會透過X(@Tomanegi0707)和BlueSky(@tomanegi0707.bsky.social)
+隨時釋出最新訊息！
+如果您能填寫問卷、關注我們的社交賬號，
+並將本作加入願望單，我們將不勝感激！</t>
+  </si>
+  <si>
+    <t>messageChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,6 +273,12 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -251,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -260,6 +310,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -540,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -549,10 +603,12 @@
     <col min="5" max="5" width="18.875" customWidth="1"/>
     <col min="6" max="6" width="22.125" customWidth="1"/>
     <col min="7" max="7" width="21.75" customWidth="1"/>
-    <col min="8" max="8" width="9" style="1"/>
+    <col min="8" max="8" width="20.5" customWidth="1"/>
+    <col min="9" max="9" width="22.75" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -574,11 +630,17 @@
       <c r="G1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="84">
+    <row r="2" spans="1:10" ht="77.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -600,8 +662,14 @@
       <c r="G2" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="397.5">
+      <c r="H2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="362.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -623,8 +691,14 @@
       <c r="G3" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
@@ -646,8 +720,14 @@
       <c r="G4" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
@@ -669,8 +749,14 @@
       <c r="G5" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
@@ -692,8 +778,14 @@
       <c r="G6" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
@@ -715,8 +807,14 @@
       <c r="G7" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="56.25">
+      <c r="H7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -738,11 +836,17 @@
       <c r="G8" s="3">
         <v>14</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="5">
+        <v>14</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="409.6">
+    <row r="9" spans="1:10" ht="392.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -764,39 +868,45 @@
       <c r="G9" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114EE9BB-2CA8-4F13-A413-5B2E1157B137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1981597-0535-4A13-AE3F-46E69ECB158F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -247,6 +247,48 @@
   <si>
     <t>messageSizeChinese02</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSpanish</t>
+  </si>
+  <si>
+    <t>messageSizeSpanish</t>
+  </si>
+  <si>
+    <t>Espacio, Intro, clic izquierdo...
+Avanzar en la conversación.</t>
+  </si>
+  <si>
+    <t>W, A, S, D o I, J, K, L... Moverse
+Shift, tecla +... Correr
+Movimiento del ratón... Mover la cámara
+Clic izquierdo... Interactuar
+Clic derecho o E o U... Usar objeto
+F o H... Encender/apagar la linterna
+P, Z o ESC... Pausar/reanudar/volver
+Ctrl, tecla ?... Girarse</t>
+  </si>
+  <si>
+    <t>Tiempo de finalización</t>
+  </si>
+  <si>
+    <t>Ensueño</t>
+  </si>
+  <si>
+    <t>Fantasía</t>
+  </si>
+  <si>
+    <t>Pesadilla</t>
+  </si>
+  <si>
+    <t>¿Volver a la pantalla de título?</t>
+  </si>
+  <si>
+    <t>¡Gracias por jugar la versión de demostración!
+Iremos compartiendo las últimas novedades
+en X (@Tomanegi0707) y BlueSky (@tomanegi0707.bsky.social).
+¡Nos encantaría que respondierais a la encuesta, nos siguierais en redes sociales
+y añadierais el juego a vuestra lista de deseos!</t>
   </si>
 </sst>
 </file>
@@ -594,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -605,10 +647,12 @@
     <col min="7" max="7" width="21.75" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
     <col min="9" max="9" width="22.75" customWidth="1"/>
-    <col min="10" max="10" width="9" style="1"/>
+    <col min="10" max="10" width="20.625" customWidth="1"/>
+    <col min="11" max="11" width="21.625" customWidth="1"/>
+    <col min="12" max="12" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -636,11 +680,17 @@
       <c r="I1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="77.25">
+    <row r="2" spans="1:12" ht="75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -668,8 +718,14 @@
       <c r="I2" s="5">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="362.25">
+      <c r="J2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="300">
       <c r="A3">
         <v>1</v>
       </c>
@@ -697,8 +753,14 @@
       <c r="I3" s="5">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>2</v>
       </c>
@@ -726,8 +788,14 @@
       <c r="I4" s="5">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>3</v>
       </c>
@@ -755,8 +823,14 @@
       <c r="I5" s="5">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="J5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>4</v>
       </c>
@@ -784,8 +858,14 @@
       <c r="I6" s="5">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="J6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>5</v>
       </c>
@@ -813,8 +893,14 @@
       <c r="I7" s="5">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="56.25">
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -842,11 +928,17 @@
       <c r="I8" s="5">
         <v>14</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="392.25">
+    <row r="9" spans="1:12" ht="337.5">
       <c r="A9">
         <v>7</v>
       </c>
@@ -874,39 +966,45 @@
       <c r="I9" s="5">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="J9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1981597-0535-4A13-AE3F-46E69ECB158F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF061BC-D419-4BC0-9697-9E8EB1441AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -289,6 +289,48 @@
 en X (@Tomanegi0707) y BlueSky (@tomanegi0707.bsky.social).
 ¡Nos encantaría que respondierais a la encuesta, nos siguierais en redes sociales
 y añadierais el juego a vuestra lista de deseos!</t>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+  </si>
+  <si>
+    <t>Espaço, Enter, clique esquerdo...
+Avançar na conversa.</t>
+  </si>
+  <si>
+    <t>W, A, S, D ou I, J, K, L... Mover
+Shift, tecla +... Correr
+Movimento do mouse... Mover a câmera
+Clique esquerdo... Interagir
+Clique direito ou E ou U... Usar item
+F ou H... Ligar/desligar a lanterna
+P, Z ou ESC... Pausar/despausar/voltar
+Ctrl, tecla ?... Virar-se</t>
+  </si>
+  <si>
+    <t>Tempo de conclusão</t>
+  </si>
+  <si>
+    <t>Devaneio</t>
+  </si>
+  <si>
+    <t>Fantasia</t>
+  </si>
+  <si>
+    <t>Pesadelo</t>
+  </si>
+  <si>
+    <t>Voltar para a tela de título?</t>
+  </si>
+  <si>
+    <t>Obrigado por jogar a versão demo!
+Vamos compartilhar as últimas novidades
+no X (@Tomanegi0707) e no BlueSky (@tomanegi0707.bsky.social)!
+Ficaríamos muito felizes se vocês respondessem à pesquisa, nos seguissem nas redes sociais
+e adicionassem o jogo à lista de desejos!</t>
   </si>
 </sst>
 </file>
@@ -636,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -649,10 +691,12 @@
     <col min="9" max="9" width="22.75" customWidth="1"/>
     <col min="10" max="10" width="20.625" customWidth="1"/>
     <col min="11" max="11" width="21.625" customWidth="1"/>
-    <col min="12" max="12" width="9" style="1"/>
+    <col min="12" max="12" width="27.75" customWidth="1"/>
+    <col min="13" max="13" width="25.625" customWidth="1"/>
+    <col min="14" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -686,11 +730,17 @@
       <c r="K1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="75">
+    <row r="2" spans="1:14" ht="75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -724,8 +774,14 @@
       <c r="K2">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="300">
+      <c r="L2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="300">
       <c r="A3">
         <v>1</v>
       </c>
@@ -759,8 +815,14 @@
       <c r="K3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2</v>
       </c>
@@ -794,8 +856,14 @@
       <c r="K4">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="L4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>3</v>
       </c>
@@ -829,8 +897,14 @@
       <c r="K5">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="L5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>4</v>
       </c>
@@ -864,8 +938,14 @@
       <c r="K6">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="L6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>5</v>
       </c>
@@ -899,8 +979,14 @@
       <c r="K7">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="56.25">
+      <c r="L7" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -934,11 +1020,17 @@
       <c r="K8">
         <v>14</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="337.5">
+    <row r="9" spans="1:14" ht="337.5">
       <c r="A9">
         <v>7</v>
       </c>
@@ -972,39 +1064,45 @@
       <c r="K9">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="L9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF061BC-D419-4BC0-9697-9E8EB1441AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F5AF61-7BF2-4C66-94B7-BFD5BE86684D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,6 +259,60 @@
 Avanzar en la conversación.</t>
   </si>
   <si>
+    <t>Tiempo de finalización</t>
+  </si>
+  <si>
+    <t>Ensueño</t>
+  </si>
+  <si>
+    <t>Fantasía</t>
+  </si>
+  <si>
+    <t>Pesadilla</t>
+  </si>
+  <si>
+    <t>¿Volver a la pantalla de título?</t>
+  </si>
+  <si>
+    <t>¡Gracias por jugar la versión de demostración!
+Iremos compartiendo las últimas novedades
+en X (@Tomanegi0707) y BlueSky (@tomanegi0707.bsky.social).
+¡Nos encantaría que respondierais a la encuesta, nos siguierais en redes sociales
+y añadierais el juego a vuestra lista de deseos!</t>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+  </si>
+  <si>
+    <t>Espaço, Enter, clique esquerdo...
+Avançar na conversa.</t>
+  </si>
+  <si>
+    <t>Tempo de conclusão</t>
+  </si>
+  <si>
+    <t>Devaneio</t>
+  </si>
+  <si>
+    <t>Fantasia</t>
+  </si>
+  <si>
+    <t>Pesadelo</t>
+  </si>
+  <si>
+    <t>Voltar para a tela de título?</t>
+  </si>
+  <si>
+    <t>Obrigado por jogar a versão demo!
+Vamos compartilhar as últimas novidades
+no X (@Tomanegi0707) e no BlueSky (@tomanegi0707.bsky.social)!
+Ficaríamos muito felizes se vocês respondessem à pesquisa, nos seguissem nas redes sociais
+e adicionassem o jogo à lista de desejos!</t>
+  </si>
+  <si>
     <t>W, A, S, D o I, J, K, L... Moverse
 Shift, tecla +... Correr
 Movimiento del ratón... Mover la cámara
@@ -267,38 +321,7 @@
 F o H... Encender/apagar la linterna
 P, Z o ESC... Pausar/reanudar/volver
 Ctrl, tecla ?... Girarse</t>
-  </si>
-  <si>
-    <t>Tiempo de finalización</t>
-  </si>
-  <si>
-    <t>Ensueño</t>
-  </si>
-  <si>
-    <t>Fantasía</t>
-  </si>
-  <si>
-    <t>Pesadilla</t>
-  </si>
-  <si>
-    <t>¿Volver a la pantalla de título?</t>
-  </si>
-  <si>
-    <t>¡Gracias por jugar la versión de demostración!
-Iremos compartiendo las últimas novedades
-en X (@Tomanegi0707) y BlueSky (@tomanegi0707.bsky.social).
-¡Nos encantaría que respondierais a la encuesta, nos siguierais en redes sociales
-y añadierais el juego a vuestra lista de deseos!</t>
-  </si>
-  <si>
-    <t>messagePortuguese</t>
-  </si>
-  <si>
-    <t>messageSizePortuguese</t>
-  </si>
-  <si>
-    <t>Espaço, Enter, clique esquerdo...
-Avançar na conversa.</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>W, A, S, D ou I, J, K, L... Mover
@@ -309,28 +332,7 @@
 F ou H... Ligar/desligar a lanterna
 P, Z ou ESC... Pausar/despausar/voltar
 Ctrl, tecla ?... Virar-se</t>
-  </si>
-  <si>
-    <t>Tempo de conclusão</t>
-  </si>
-  <si>
-    <t>Devaneio</t>
-  </si>
-  <si>
-    <t>Fantasia</t>
-  </si>
-  <si>
-    <t>Pesadelo</t>
-  </si>
-  <si>
-    <t>Voltar para a tela de título?</t>
-  </si>
-  <si>
-    <t>Obrigado por jogar a versão demo!
-Vamos compartilhar as últimas novidades
-no X (@Tomanegi0707) e no BlueSky (@tomanegi0707.bsky.social)!
-Ficaríamos muito felizes se vocês respondessem à pesquisa, nos seguissem nas redes sociais
-e adicionassem o jogo à lista de desejos!</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -731,10 +733,10 @@
         <v>44</v>
       </c>
       <c r="L1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" t="s">
         <v>53</v>
-      </c>
-      <c r="M1" t="s">
-        <v>54</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>15</v>
@@ -772,13 +774,13 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="300">
@@ -810,16 +812,16 @@
         <v>12</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -851,13 +853,13 @@
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K4">
         <v>16</v>
       </c>
       <c r="L4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M4">
         <v>16</v>
@@ -892,13 +894,13 @@
         <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K5">
         <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M5">
         <v>32</v>
@@ -933,13 +935,13 @@
         <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K6">
         <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M6">
         <v>32</v>
@@ -974,13 +976,13 @@
         <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K7">
         <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -1015,13 +1017,13 @@
         <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K8">
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M8">
         <v>14</v>
@@ -1059,13 +1061,13 @@
         <v>20</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K9">
         <v>20</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M9">
         <v>20</v>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F5AF61-7BF2-4C66-94B7-BFD5BE86684D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C792A13-A9E6-4A14-887F-13F15279A9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -856,13 +856,13 @@
         <v>46</v>
       </c>
       <c r="K4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L4" t="s">
         <v>55</v>
       </c>
       <c r="M4">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1064,13 +1064,13 @@
         <v>51</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>60</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:14">

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C792A13-A9E6-4A14-887F-13F15279A9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DDE556-CE07-4423-A9B2-885286DE5EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -334,12 +334,42 @@
 Ctrl, tecla ?... Virar-se</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>本当にセーブデータを削除しますか？
+(一度削除したデータは元に戻せません)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Are you sure you want to delete your save data?
+(Deleted data cannot be recovered.)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>确定要删除存档吗？
+（数据一经删除将无法恢复）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確定要刪除存檔嗎？
+（資料一經刪除即無法復原）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>¿Seguro que quieres borrar los datos guardados?
+(Una vez borrados, los datos no se podrán recuperar.)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tem certeza de que deseja excluir os dados salvos?
+(Uma vez excluídos, os dados não poderão ser recuperados.)</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +396,13 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -387,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -400,6 +437,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1073,8 +1113,44 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" ht="112.5">
       <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10">
+        <v>14</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10">
         <v>8</v>
       </c>
     </row>
